--- a/src/test/resources/testdata/LoginData.xlsx
+++ b/src/test/resources/testdata/LoginData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\IdeaProjects\MyAutomation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257B6794-0129-4FF7-9785-1B7492D50432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633FBD0E-2917-4135-B83D-D1E495D6327B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1C270E7D-8191-456C-8553-E01684361388}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1C270E7D-8191-456C-8553-E01684361388}"/>
   </bookViews>
   <sheets>
     <sheet name="credentials" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>UserName</t>
   </si>
@@ -56,6 +56,18 @@
   </si>
   <si>
     <t>WebPage</t>
+  </si>
+  <si>
+    <t>rahulshettyacademy</t>
+  </si>
+  <si>
+    <t>https://rahulshettyacademy.com/dropdownsPractise/</t>
+  </si>
+  <si>
+    <t>https://rahulshettyacademy.com/upload-download-test/</t>
+  </si>
+  <si>
+    <t>rahulshettyacademyUpload</t>
   </si>
 </sst>
 </file>
@@ -133,7 +145,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -156,6 +168,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -510,11 +523,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941094CB-738B-4225-A171-1528432CAB3D}">
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="33.5546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="75.77734375" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -533,9 +546,27 @@
         <v>8</v>
       </c>
     </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B2" r:id="rId1" xr:uid="{277DFFE5-1F11-4F4C-9F68-C7C3461BFBFE}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{BA7C6CF2-1C2A-4347-939D-FD4A6681B255}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{FDFFF78C-1BDF-419E-8969-C30CA3E5F87F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/testdata/LoginData.xlsx
+++ b/src/test/resources/testdata/LoginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\IdeaProjects\MyAutomation\src\test\resources\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{633FBD0E-2917-4135-B83D-D1E495D6327B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50838E20-396C-4EC1-BEFF-C2A0C6C0750C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{1C270E7D-8191-456C-8553-E01684361388}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>UserName</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>rahulshettyacademyUpload</t>
+  </si>
+  <si>
+    <t>Amazon</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/</t>
   </si>
 </sst>
 </file>
@@ -145,7 +151,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -157,18 +163,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -523,15 +528,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{941094CB-738B-4225-A171-1528432CAB3D}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="33.5546875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="87.109375" customWidth="1"/>
+    <col min="1" max="1" width="33.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="87.109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B1" s="4" t="s">
@@ -539,27 +544,35 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="6" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
